--- a/Results/Errors_everything.xlsx
+++ b/Results/Errors_everything.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4635A3-B39E-45A4-AD9F-A92C04254B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DD6356-5858-406C-AE96-70FC40CE5989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="1104" windowWidth="23136" windowHeight="11136" xr2:uid="{900DFFDC-2DE1-4004-B463-95FC19C37CCD}"/>
+    <workbookView xWindow="2988" yWindow="1956" windowWidth="17280" windowHeight="9036" activeTab="1" xr2:uid="{900DFFDC-2DE1-4004-B463-95FC19C37CCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -550,19 +550,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144F125D-3998-4A51-B48A-FC26F18A6173}">
   <dimension ref="A1:I42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.88671875" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" customWidth="1"/>
+    <col min="7" max="7" width="23.88671875" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" customWidth="1"/>
     <col min="9" max="9" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>1</v>
       </c>
@@ -615,7 +615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -644,7 +644,7 @@
         <v>4.1749999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -673,7 +673,7 @@
         <v>29.274999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -702,7 +702,7 @@
         <v>13.19</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -760,7 +760,7 @@
         <v>13.17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -789,7 +789,7 @@
         <v>68.36</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -818,7 +818,7 @@
         <v>66.09</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -847,7 +847,7 @@
         <v>34.365000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -876,7 +876,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,10 +905,10 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>17</v>
       </c>
@@ -916,7 +916,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>9</v>
       </c>
@@ -924,7 +924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -935,7 +935,7 @@
         <v>3.7250000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>2</v>
       </c>
@@ -946,7 +946,7 @@
         <v>32.475000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -957,7 +957,7 @@
         <v>12.955</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
@@ -979,7 +979,7 @@
         <v>13.17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -990,7 +990,7 @@
         <v>80.534999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>64.040000000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>34.365000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>17.559999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
@@ -1034,17 +1034,17 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>3.7250000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>2</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>32.465000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>3</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>12.955</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>16</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>13.17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>80.504999999999995</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>64.040000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>34.365000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>8</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>17.559999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>9</v>
       </c>
@@ -1132,19 +1132,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C94FF787-77DB-49E6-B40F-1204D3E5E312}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5703125" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" customWidth="1"/>
+    <col min="11" max="11" width="22.5546875" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1182,7 +1184,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1220,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1258,7 +1260,7 @@
         <v>3.7250000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
@@ -1296,7 +1298,7 @@
         <v>32.465000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
@@ -1334,7 +1336,7 @@
         <v>12.955</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1372,7 +1374,7 @@
         <v>13.17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
@@ -1410,7 +1412,7 @@
         <v>80.504999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -1448,7 +1450,7 @@
         <v>64.040000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1486,7 +1488,7 @@
         <v>34.365000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1524,7 +1526,7 @@
         <v>17.559999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1562,7 +1564,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1579,7 +1581,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,10 +1595,8 @@
         <v>0</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1604,16 +1604,14 @@
         <v>3.63</v>
       </c>
       <c r="C16" s="2">
-        <v>3.7250000000000001</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3.7250000000000001</v>
+        <v>13.29</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5.51</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1621,16 +1619,14 @@
         <v>28.664999999999999</v>
       </c>
       <c r="C17" s="2">
-        <v>32.475000000000001</v>
-      </c>
-      <c r="D17" s="2">
-        <v>32.465000000000003</v>
+        <v>31.02</v>
+      </c>
+      <c r="D17" s="1">
+        <v>34.854999999999997</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
@@ -1638,16 +1634,15 @@
         <v>13.19</v>
       </c>
       <c r="C18" s="2">
-        <v>12.955</v>
+        <v>17.425000000000001</v>
       </c>
       <c r="D18" s="2">
-        <v>12.955</v>
+        <v>16.535</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -1657,14 +1652,12 @@
       <c r="C19" s="2">
         <v>13.17</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>13.17</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -1672,16 +1665,14 @@
         <v>68.36</v>
       </c>
       <c r="C20" s="2">
-        <v>80.534999999999997</v>
-      </c>
-      <c r="D20" s="2">
-        <v>80.504999999999995</v>
+        <v>79.81</v>
+      </c>
+      <c r="D20" s="1">
+        <v>80.424999999999997</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -1689,16 +1680,14 @@
         <v>64.040000000000006</v>
       </c>
       <c r="C21" s="2">
-        <v>64.040000000000006</v>
-      </c>
-      <c r="D21" s="2">
-        <v>64.040000000000006</v>
+        <v>53.034999999999997</v>
+      </c>
+      <c r="D21" s="1">
+        <v>66.59</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1706,16 +1695,14 @@
         <v>34.365000000000002</v>
       </c>
       <c r="C22" s="2">
-        <v>34.365000000000002</v>
-      </c>
-      <c r="D22" s="2">
-        <v>34.365000000000002</v>
+        <v>26.844999999999999</v>
+      </c>
+      <c r="D22" s="1">
+        <v>34.484999999999999</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -1723,16 +1710,14 @@
         <v>17.559999999999999</v>
       </c>
       <c r="C23" s="2">
-        <v>17.559999999999999</v>
-      </c>
-      <c r="D23" s="2">
-        <v>17.559999999999999</v>
+        <v>21.49</v>
+      </c>
+      <c r="D23" s="1">
+        <v>24.79</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -1742,56 +1727,54 @@
       <c r="C24" s="2">
         <v>30.75</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>30.75</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
     </row>
   </sheetData>
